--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Panchos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4702F03-1F0B-4B9A-9A15-CDBDB1CF301E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BB7CC1-1524-4A72-9046-B46DD33B16BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6111,10 +6111,10 @@
         <v>28</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H199" s="2">
-        <v>0</v>
+        <v>2.4467592592592593E-2</v>
       </c>
       <c r="I199" s="1">
         <v>46174.604745370372</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Panchos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0B4E941-14BF-4AC5-9465-5304FF965CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A48747A6-6C24-467D-B934-F04DB347D941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="43">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,13 +86,25 @@
     <t>Mark Complete</t>
   </si>
   <si>
+    <t>(Spanish) Scene of an Accident</t>
+  </si>
+  <si>
+    <t>(Spanish) -Alert Driving</t>
+  </si>
+  <si>
+    <t>(Spanish) Space Management</t>
+  </si>
+  <si>
+    <t>(Spanish) Winter Weather</t>
+  </si>
+  <si>
+    <t>(Spanish) Rules for Safe Driving</t>
+  </si>
+  <si>
     <t>Pancho's Transportation</t>
   </si>
   <si>
     <t>ALFREDO LOERA</t>
-  </si>
-  <si>
-    <t>(Spanish) Space Management</t>
   </si>
   <si>
     <t>CRESCENCIO LOPEZ</t>
@@ -125,16 +137,10 @@
     <t>(Spanish) In Cab Distractions</t>
   </si>
   <si>
-    <t>(Spanish) -Alert Driving</t>
-  </si>
-  <si>
     <t>(Spanish) Micro-Learn-Camera Obstruction Facts</t>
   </si>
   <si>
     <t>(Spanish) Aggressive Driving</t>
-  </si>
-  <si>
-    <t>(Spanish) Rules for Safe Driving</t>
   </si>
   <si>
     <t>(Spanish) Driver Health</t>
@@ -149,9 +155,6 @@
     <t>PEDRO HERNANDEZ</t>
   </si>
   <si>
-    <t>(Spanish) Scene of an Accident</t>
-  </si>
-  <si>
     <t>(Spanish) Safe Following</t>
   </si>
   <si>
@@ -161,10 +164,10 @@
     <t>(Spanish) Short distracted Driving</t>
   </si>
   <si>
-    <t>(Spanish) Winter Weather</t>
+    <t>(SP) 3 Points of Contact</t>
   </si>
   <si>
-    <t>(SP) 3 Points of Contact</t>
+    <t>(Spanish) Camera Management (Onboarding)</t>
   </si>
 </sst>
 </file>
@@ -538,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -587,13 +590,13 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>2464</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>17</v>
@@ -616,13 +619,13 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E3">
         <v>2465</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>17</v>
@@ -645,13 +648,13 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <v>2463</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>17</v>
@@ -674,13 +677,13 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>2468</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>17</v>
@@ -703,13 +706,13 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>2466</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>17</v>
@@ -732,13 +735,13 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>2467</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>17</v>
@@ -761,13 +764,13 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E8">
         <v>2460</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>17</v>
@@ -790,13 +793,13 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E9">
         <v>2461</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>17</v>
@@ -819,13 +822,13 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E10">
         <v>2462</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>17</v>
@@ -848,16 +851,16 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E11">
         <v>2464</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -877,16 +880,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E12">
         <v>2465</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -906,16 +909,16 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E13">
         <v>2463</v>
       </c>
       <c r="F13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -935,16 +938,16 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E14">
         <v>2468</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -964,16 +967,16 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E15">
         <v>2466</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -993,16 +996,16 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E16">
         <v>2467</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1022,16 +1025,16 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E17">
         <v>2460</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1051,16 +1054,16 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E18">
         <v>2461</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>12</v>
@@ -1089,16 +1092,16 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E20">
         <v>2462</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -1118,16 +1121,16 @@
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E21">
         <v>2464</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -1147,16 +1150,16 @@
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E22">
         <v>2465</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>12</v>
@@ -1185,16 +1188,16 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E24">
         <v>2463</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>12</v>
@@ -1223,16 +1226,16 @@
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E26">
         <v>2468</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>12</v>
@@ -1261,16 +1264,16 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E28">
         <v>2466</v>
       </c>
       <c r="F28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>12</v>
@@ -1299,16 +1302,16 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E30">
         <v>2467</v>
       </c>
       <c r="F30" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>10</v>
@@ -1328,16 +1331,16 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E31">
         <v>2460</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>13</v>
@@ -1357,16 +1360,16 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E32">
         <v>2461</v>
       </c>
       <c r="F32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
@@ -1386,16 +1389,16 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E33">
         <v>2462</v>
       </c>
       <c r="F33" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
@@ -1415,16 +1418,16 @@
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E34">
         <v>2464</v>
       </c>
       <c r="F34" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
@@ -1444,16 +1447,16 @@
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E35">
         <v>2465</v>
       </c>
       <c r="F35" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>10</v>
@@ -1473,16 +1476,16 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E36">
         <v>2463</v>
       </c>
       <c r="F36" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
@@ -1502,16 +1505,16 @@
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E37">
         <v>2468</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>12</v>
@@ -1540,16 +1543,16 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E39">
         <v>2466</v>
       </c>
       <c r="F39" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1569,16 +1572,16 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E40">
         <v>2467</v>
       </c>
       <c r="F40" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
@@ -1598,16 +1601,16 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E41">
         <v>2460</v>
       </c>
       <c r="F41" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
@@ -1627,16 +1630,16 @@
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E42">
         <v>2461</v>
       </c>
       <c r="F42" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>10</v>
@@ -1656,16 +1659,16 @@
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E43">
         <v>2462</v>
       </c>
       <c r="F43" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
@@ -1685,16 +1688,16 @@
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E44">
         <v>2464</v>
       </c>
       <c r="F44" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>10</v>
@@ -1714,16 +1717,16 @@
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E45">
         <v>2465</v>
       </c>
       <c r="F45" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1743,16 +1746,16 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E46">
         <v>2463</v>
       </c>
       <c r="F46" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>12</v>
@@ -1781,16 +1784,16 @@
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E48">
         <v>2468</v>
       </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -1810,16 +1813,16 @@
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E49">
         <v>2466</v>
       </c>
       <c r="F49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>10</v>
@@ -1839,16 +1842,16 @@
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E50">
         <v>2467</v>
       </c>
       <c r="F50" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
@@ -1868,16 +1871,16 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E51">
         <v>2460</v>
       </c>
       <c r="F51" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>10</v>
@@ -1897,16 +1900,16 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E52">
         <v>2461</v>
       </c>
       <c r="F52" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -1926,16 +1929,16 @@
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E53">
         <v>2462</v>
       </c>
       <c r="F53" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>10</v>
@@ -1955,16 +1958,16 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E54">
         <v>2464</v>
       </c>
       <c r="F54" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>10</v>
@@ -1984,16 +1987,16 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E55">
         <v>2465</v>
       </c>
       <c r="F55" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2013,16 +2016,16 @@
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E56">
         <v>2463</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>10</v>
@@ -2042,16 +2045,16 @@
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E57">
         <v>2468</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
@@ -2071,16 +2074,16 @@
     </row>
     <row r="58" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E58">
         <v>2466</v>
       </c>
       <c r="F58" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
@@ -2100,16 +2103,16 @@
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E59">
         <v>2467</v>
       </c>
       <c r="F59" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>10</v>
@@ -2129,16 +2132,16 @@
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E60">
         <v>2460</v>
       </c>
       <c r="F60" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -2158,16 +2161,16 @@
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E61">
         <v>2461</v>
       </c>
       <c r="F61" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>10</v>
@@ -2187,16 +2190,16 @@
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E62">
         <v>2462</v>
       </c>
       <c r="F62" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>10</v>
@@ -2216,16 +2219,16 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E63">
         <v>2464</v>
       </c>
       <c r="F63" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>10</v>
@@ -2245,16 +2248,16 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E64">
         <v>2465</v>
       </c>
       <c r="F64" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -2274,16 +2277,16 @@
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E65">
         <v>2463</v>
       </c>
       <c r="F65" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2303,16 +2306,16 @@
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E66">
         <v>2468</v>
       </c>
       <c r="F66" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>10</v>
@@ -2332,16 +2335,16 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E67">
         <v>2466</v>
       </c>
       <c r="F67" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>10</v>
@@ -2361,16 +2364,16 @@
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D68" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E68">
         <v>2467</v>
       </c>
       <c r="F68" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>10</v>
@@ -2390,16 +2393,16 @@
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E69">
         <v>2460</v>
       </c>
       <c r="F69" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2419,16 +2422,16 @@
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E70">
         <v>2461</v>
       </c>
       <c r="F70" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2448,16 +2451,16 @@
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E71">
         <v>2462</v>
       </c>
       <c r="F71" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>10</v>
@@ -2477,16 +2480,16 @@
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D72" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E72">
         <v>2464</v>
       </c>
       <c r="F72" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>10</v>
@@ -2506,16 +2509,16 @@
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E73">
         <v>2465</v>
       </c>
       <c r="F73" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>10</v>
@@ -2535,16 +2538,16 @@
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E74">
         <v>2463</v>
       </c>
       <c r="F74" t="s">
+        <v>23</v>
+      </c>
+      <c r="H74" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2564,16 +2567,16 @@
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E75">
         <v>2468</v>
       </c>
       <c r="F75" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>10</v>
@@ -2593,16 +2596,16 @@
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D76" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E76">
         <v>2466</v>
       </c>
       <c r="F76" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>10</v>
@@ -2622,16 +2625,16 @@
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E77">
         <v>2467</v>
       </c>
       <c r="F77" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>10</v>
@@ -2651,16 +2654,16 @@
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E78">
         <v>2460</v>
       </c>
       <c r="F78" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>10</v>
@@ -2680,16 +2683,16 @@
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E79">
         <v>2461</v>
       </c>
       <c r="F79" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>10</v>
@@ -2709,16 +2712,16 @@
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E80">
         <v>2462</v>
       </c>
       <c r="F80" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -2738,16 +2741,16 @@
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E81">
         <v>2464</v>
       </c>
       <c r="F81" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -2767,16 +2770,16 @@
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E82">
         <v>2465</v>
       </c>
       <c r="F82" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2796,16 +2799,16 @@
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E83">
         <v>2463</v>
       </c>
       <c r="F83" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>10</v>
@@ -2825,16 +2828,16 @@
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E84">
         <v>2468</v>
       </c>
       <c r="F84" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2854,16 +2857,16 @@
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E85">
         <v>2466</v>
       </c>
       <c r="F85" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -2883,16 +2886,16 @@
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E86">
         <v>2467</v>
       </c>
       <c r="F86" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>10</v>
@@ -2912,16 +2915,16 @@
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E87">
         <v>2460</v>
       </c>
       <c r="F87" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>10</v>
@@ -2941,16 +2944,16 @@
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E88">
         <v>2461</v>
       </c>
       <c r="F88" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -2970,16 +2973,16 @@
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D89" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E89">
         <v>2462</v>
       </c>
       <c r="F89" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>10</v>
@@ -2999,16 +3002,16 @@
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E90">
         <v>2464</v>
       </c>
       <c r="F90" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>10</v>
@@ -3028,16 +3031,16 @@
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E91">
         <v>2465</v>
       </c>
       <c r="F91" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>10</v>
@@ -3057,16 +3060,16 @@
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E92">
         <v>2463</v>
       </c>
       <c r="F92" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>10</v>
@@ -3086,16 +3089,16 @@
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D93" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E93">
         <v>2468</v>
       </c>
       <c r="F93" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>10</v>
@@ -3115,16 +3118,16 @@
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E94">
         <v>3681</v>
       </c>
       <c r="F94" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>10</v>
@@ -3144,16 +3147,16 @@
     </row>
     <row r="95" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D95" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E95">
         <v>2466</v>
       </c>
       <c r="F95" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>10</v>
@@ -3173,16 +3176,16 @@
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D96" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E96">
         <v>2467</v>
       </c>
       <c r="F96" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>10</v>
@@ -3202,16 +3205,16 @@
     </row>
     <row r="97" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E97">
         <v>2460</v>
       </c>
       <c r="F97" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>10</v>
@@ -3231,16 +3234,16 @@
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E98">
         <v>3533</v>
       </c>
       <c r="F98" t="s">
+        <v>37</v>
+      </c>
+      <c r="H98" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3260,16 +3263,16 @@
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E99">
         <v>2462</v>
       </c>
       <c r="F99" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>10</v>
@@ -3289,16 +3292,16 @@
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D100" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E100">
         <v>2464</v>
       </c>
       <c r="F100" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>10</v>
@@ -3318,16 +3321,16 @@
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D101" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E101">
         <v>2465</v>
       </c>
       <c r="F101" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>10</v>
@@ -3347,16 +3350,16 @@
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E102">
         <v>2463</v>
       </c>
       <c r="F102" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>10</v>
@@ -3376,16 +3379,16 @@
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E103">
         <v>2468</v>
       </c>
       <c r="F103" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>10</v>
@@ -3405,16 +3408,16 @@
     </row>
     <row r="104" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E104">
         <v>3681</v>
       </c>
       <c r="F104" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>10</v>
@@ -3434,16 +3437,16 @@
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E105">
         <v>2466</v>
       </c>
       <c r="F105" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>10</v>
@@ -3463,16 +3466,16 @@
     </row>
     <row r="106" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E106">
         <v>2467</v>
       </c>
       <c r="F106" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>10</v>
@@ -3492,16 +3495,16 @@
     </row>
     <row r="107" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E107">
         <v>2460</v>
       </c>
       <c r="F107" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>10</v>
@@ -3521,16 +3524,16 @@
     </row>
     <row r="108" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D108" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E108">
         <v>3533</v>
       </c>
       <c r="F108" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>10</v>
@@ -3550,16 +3553,16 @@
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E109">
         <v>2462</v>
       </c>
       <c r="F109" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>10</v>
@@ -3579,16 +3582,16 @@
     </row>
     <row r="110" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D110" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E110">
         <v>2464</v>
       </c>
       <c r="F110" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>10</v>
@@ -3608,16 +3611,16 @@
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E111">
         <v>2465</v>
       </c>
       <c r="F111" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>10</v>
@@ -3637,16 +3640,16 @@
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E112">
         <v>2463</v>
       </c>
       <c r="F112" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>10</v>
@@ -3666,16 +3669,16 @@
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E113">
         <v>2468</v>
       </c>
       <c r="F113" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>10</v>
@@ -3695,16 +3698,16 @@
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D114" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E114">
         <v>3681</v>
       </c>
       <c r="F114" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>10</v>
@@ -3724,16 +3727,16 @@
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E115">
         <v>2466</v>
       </c>
       <c r="F115" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>10</v>
@@ -3753,16 +3756,16 @@
     </row>
     <row r="116" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E116">
         <v>2467</v>
       </c>
       <c r="F116" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>10</v>
@@ -3782,16 +3785,16 @@
     </row>
     <row r="117" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D117" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E117">
         <v>2460</v>
       </c>
       <c r="F117" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>10</v>
@@ -3811,16 +3814,16 @@
     </row>
     <row r="118" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D118" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E118">
         <v>3533</v>
       </c>
       <c r="F118" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>10</v>
@@ -3840,16 +3843,16 @@
     </row>
     <row r="119" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D119" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E119">
         <v>2462</v>
       </c>
       <c r="F119" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>10</v>
@@ -3869,16 +3872,16 @@
     </row>
     <row r="120" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D120" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E120">
         <v>2468</v>
       </c>
       <c r="F120" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>13</v>
@@ -3898,16 +3901,16 @@
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E121">
         <v>2464</v>
       </c>
       <c r="F121" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>10</v>
@@ -3927,16 +3930,16 @@
     </row>
     <row r="122" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E122">
         <v>2465</v>
       </c>
       <c r="F122" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -3956,16 +3959,16 @@
     </row>
     <row r="123" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D123" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E123">
         <v>2463</v>
       </c>
       <c r="F123" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>10</v>
@@ -3985,16 +3988,16 @@
     </row>
     <row r="124" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E124">
         <v>3681</v>
       </c>
       <c r="F124" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>10</v>
@@ -4014,16 +4017,16 @@
     </row>
     <row r="125" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E125">
         <v>2466</v>
       </c>
       <c r="F125" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>10</v>
@@ -4043,16 +4046,16 @@
     </row>
     <row r="126" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E126">
         <v>2467</v>
       </c>
       <c r="F126" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -4072,16 +4075,16 @@
     </row>
     <row r="127" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D127" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E127">
         <v>2460</v>
       </c>
       <c r="F127" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>10</v>
@@ -4101,16 +4104,16 @@
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E128">
         <v>3533</v>
       </c>
       <c r="F128" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>10</v>
@@ -4130,16 +4133,16 @@
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E129">
         <v>2462</v>
       </c>
       <c r="F129" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>10</v>
@@ -4159,16 +4162,16 @@
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E130">
         <v>2464</v>
       </c>
       <c r="F130" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>10</v>
@@ -4188,16 +4191,16 @@
     </row>
     <row r="131" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E131">
         <v>2465</v>
       </c>
       <c r="F131" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>10</v>
@@ -4217,16 +4220,16 @@
     </row>
     <row r="132" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D132" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E132">
         <v>2463</v>
       </c>
       <c r="F132" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>10</v>
@@ -4246,16 +4249,16 @@
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E133">
         <v>2468</v>
       </c>
       <c r="F133" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>10</v>
@@ -4275,16 +4278,16 @@
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E134">
         <v>2466</v>
       </c>
       <c r="F134" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4304,16 +4307,16 @@
     </row>
     <row r="135" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E135">
         <v>2467</v>
       </c>
       <c r="F135" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>10</v>
@@ -4333,16 +4336,16 @@
     </row>
     <row r="136" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D136" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E136">
         <v>2460</v>
       </c>
       <c r="F136" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>10</v>
@@ -4362,16 +4365,16 @@
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E137">
         <v>3533</v>
       </c>
       <c r="F137" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>10</v>
@@ -4391,16 +4394,16 @@
     </row>
     <row r="138" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E138">
         <v>2462</v>
       </c>
       <c r="F138" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>10</v>
@@ -4420,16 +4423,16 @@
     </row>
     <row r="139" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D139" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E139">
         <v>2464</v>
       </c>
       <c r="F139" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>10</v>
@@ -4449,16 +4452,16 @@
     </row>
     <row r="140" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D140" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E140">
         <v>2465</v>
       </c>
       <c r="F140" t="s">
+        <v>22</v>
+      </c>
+      <c r="H140" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>10</v>
@@ -4478,16 +4481,16 @@
     </row>
     <row r="141" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E141">
         <v>2463</v>
       </c>
       <c r="F141" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>10</v>
@@ -4507,16 +4510,16 @@
     </row>
     <row r="142" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D142" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E142">
         <v>2468</v>
       </c>
       <c r="F142" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>10</v>
@@ -4536,16 +4539,16 @@
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D143" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E143">
         <v>2466</v>
       </c>
       <c r="F143" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>10</v>
@@ -4565,16 +4568,16 @@
     </row>
     <row r="144" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D144" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E144">
         <v>2467</v>
       </c>
       <c r="F144" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>10</v>
@@ -4594,16 +4597,16 @@
     </row>
     <row r="145" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D145" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E145">
         <v>2460</v>
       </c>
       <c r="F145" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>10</v>
@@ -4623,16 +4626,16 @@
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D146" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E146">
         <v>3533</v>
       </c>
       <c r="F146" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>10</v>
@@ -4652,16 +4655,16 @@
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D147" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E147">
         <v>2462</v>
       </c>
       <c r="F147" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>10</v>
@@ -4681,13 +4684,13 @@
     </row>
     <row r="148" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D148" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E148">
         <v>2464</v>
       </c>
       <c r="F148" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>17</v>
@@ -4710,13 +4713,13 @@
     </row>
     <row r="149" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E149">
         <v>2465</v>
       </c>
       <c r="F149" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>17</v>
@@ -4748,13 +4751,13 @@
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E151">
         <v>2463</v>
       </c>
       <c r="F151" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>17</v>
@@ -4777,13 +4780,13 @@
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E152">
         <v>2468</v>
       </c>
       <c r="F152" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>17</v>
@@ -4806,13 +4809,13 @@
     </row>
     <row r="153" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E153">
         <v>2466</v>
       </c>
       <c r="F153" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>17</v>
@@ -4835,13 +4838,13 @@
     </row>
     <row r="154" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D154" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E154">
         <v>2467</v>
       </c>
       <c r="F154" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>17</v>
@@ -4864,13 +4867,13 @@
     </row>
     <row r="155" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D155" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E155">
         <v>2460</v>
       </c>
       <c r="F155" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>17</v>
@@ -4893,13 +4896,13 @@
     </row>
     <row r="156" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D156" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E156">
         <v>3533</v>
       </c>
       <c r="F156" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>17</v>
@@ -4922,13 +4925,13 @@
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D157" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E157">
         <v>2462</v>
       </c>
       <c r="F157" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>17</v>
@@ -4951,13 +4954,13 @@
     </row>
     <row r="158" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D158" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E158">
         <v>2464</v>
       </c>
       <c r="F158" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>41</v>
@@ -4980,13 +4983,13 @@
     </row>
     <row r="159" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D159" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E159">
         <v>2465</v>
       </c>
       <c r="F159" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>41</v>
@@ -5009,13 +5012,13 @@
     </row>
     <row r="160" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E160">
         <v>2463</v>
       </c>
       <c r="F160" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>41</v>
@@ -5038,13 +5041,13 @@
     </row>
     <row r="161" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D161" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E161">
         <v>2468</v>
       </c>
       <c r="F161" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>41</v>
@@ -5067,13 +5070,13 @@
     </row>
     <row r="162" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E162">
         <v>2466</v>
       </c>
       <c r="F162" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>41</v>
@@ -5096,13 +5099,13 @@
     </row>
     <row r="163" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D163" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E163">
         <v>2467</v>
       </c>
       <c r="F163" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>41</v>
@@ -5125,13 +5128,13 @@
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D164" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E164">
         <v>2460</v>
       </c>
       <c r="F164" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>41</v>
@@ -5154,13 +5157,13 @@
     </row>
     <row r="165" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D165" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E165">
         <v>3533</v>
       </c>
       <c r="F165" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>41</v>
@@ -5192,13 +5195,13 @@
     </row>
     <row r="167" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D167" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E167">
         <v>2462</v>
       </c>
       <c r="F167" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>41</v>
@@ -5221,16 +5224,16 @@
     </row>
     <row r="168" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D168" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E168">
         <v>2464</v>
       </c>
       <c r="F168" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>10</v>
@@ -5250,16 +5253,16 @@
     </row>
     <row r="169" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D169" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E169">
         <v>2465</v>
       </c>
       <c r="F169" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>10</v>
@@ -5279,16 +5282,16 @@
     </row>
     <row r="170" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D170" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E170">
         <v>2463</v>
       </c>
       <c r="F170" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>10</v>
@@ -5308,16 +5311,16 @@
     </row>
     <row r="171" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D171" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E171">
         <v>2468</v>
       </c>
       <c r="F171" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>10</v>
@@ -5337,16 +5340,16 @@
     </row>
     <row r="172" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D172" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E172">
         <v>2466</v>
       </c>
       <c r="F172" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>10</v>
@@ -5366,16 +5369,16 @@
     </row>
     <row r="173" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D173" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E173">
         <v>2467</v>
       </c>
       <c r="F173" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>10</v>
@@ -5395,16 +5398,16 @@
     </row>
     <row r="174" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D174" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E174">
         <v>2460</v>
       </c>
       <c r="F174" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>10</v>
@@ -5424,16 +5427,16 @@
     </row>
     <row r="175" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D175" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E175">
         <v>3533</v>
       </c>
       <c r="F175" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>10</v>
@@ -5453,16 +5456,16 @@
     </row>
     <row r="176" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D176" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E176">
         <v>2462</v>
       </c>
       <c r="F176" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>10</v>
@@ -5482,16 +5485,16 @@
     </row>
     <row r="177" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D177" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E177">
         <v>2464</v>
       </c>
       <c r="F177" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>10</v>
@@ -5511,16 +5514,16 @@
     </row>
     <row r="178" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D178" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E178">
         <v>2465</v>
       </c>
       <c r="F178" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>10</v>
@@ -5540,16 +5543,16 @@
     </row>
     <row r="179" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D179" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E179">
         <v>2463</v>
       </c>
       <c r="F179" t="s">
+        <v>23</v>
+      </c>
+      <c r="H179" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="H179" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>10</v>
@@ -5569,16 +5572,16 @@
     </row>
     <row r="180" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D180" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E180">
         <v>2468</v>
       </c>
       <c r="F180" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>10</v>
@@ -5598,16 +5601,16 @@
     </row>
     <row r="181" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D181" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E181">
         <v>2466</v>
       </c>
       <c r="F181" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>10</v>
@@ -5627,16 +5630,16 @@
     </row>
     <row r="182" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D182" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E182">
         <v>2467</v>
       </c>
       <c r="F182" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>10</v>
@@ -5656,16 +5659,16 @@
     </row>
     <row r="183" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D183" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E183">
         <v>2460</v>
       </c>
       <c r="F183" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>12</v>
@@ -5694,16 +5697,16 @@
     </row>
     <row r="185" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D185" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E185">
         <v>3533</v>
       </c>
       <c r="F185" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>10</v>
@@ -5723,16 +5726,16 @@
     </row>
     <row r="186" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D186" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E186">
         <v>2462</v>
       </c>
       <c r="F186" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>10</v>
@@ -5752,16 +5755,16 @@
     </row>
     <row r="187" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D187" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E187">
         <v>2464</v>
       </c>
       <c r="F187" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>10</v>
@@ -5781,16 +5784,16 @@
     </row>
     <row r="188" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D188" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E188">
         <v>2465</v>
       </c>
       <c r="F188" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>10</v>
@@ -5810,16 +5813,16 @@
     </row>
     <row r="189" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D189" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E189">
         <v>2463</v>
       </c>
       <c r="F189" t="s">
+        <v>23</v>
+      </c>
+      <c r="H189" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="H189" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>10</v>
@@ -5839,16 +5842,16 @@
     </row>
     <row r="190" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D190" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E190">
         <v>2468</v>
       </c>
       <c r="F190" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>10</v>
@@ -5868,16 +5871,16 @@
     </row>
     <row r="191" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D191" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E191">
         <v>2466</v>
       </c>
       <c r="F191" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>10</v>
@@ -5897,16 +5900,16 @@
     </row>
     <row r="192" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D192" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E192">
         <v>2467</v>
       </c>
       <c r="F192" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>10</v>
@@ -5926,16 +5929,16 @@
     </row>
     <row r="193" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D193" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E193">
         <v>2460</v>
       </c>
       <c r="F193" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>10</v>
@@ -5955,16 +5958,16 @@
     </row>
     <row r="194" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D194" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E194">
         <v>3533</v>
       </c>
       <c r="F194" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>10</v>
@@ -5984,16 +5987,16 @@
     </row>
     <row r="195" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D195" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E195">
         <v>2462</v>
       </c>
       <c r="F195" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>10</v>
@@ -6013,16 +6016,16 @@
     </row>
     <row r="196" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D196" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E196">
         <v>2464</v>
       </c>
       <c r="F196" t="s">
+        <v>21</v>
+      </c>
+      <c r="H196" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H196" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>10</v>
@@ -6042,16 +6045,16 @@
     </row>
     <row r="197" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D197" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E197">
         <v>2465</v>
       </c>
       <c r="F197" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>10</v>
@@ -6071,16 +6074,16 @@
     </row>
     <row r="198" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D198" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E198">
         <v>2463</v>
       </c>
       <c r="F198" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>10</v>
@@ -6100,16 +6103,16 @@
     </row>
     <row r="199" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D199" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E199">
         <v>2468</v>
       </c>
       <c r="F199" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>10</v>
@@ -6129,16 +6132,16 @@
     </row>
     <row r="200" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D200" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E200">
         <v>2466</v>
       </c>
       <c r="F200" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>10</v>
@@ -6158,16 +6161,16 @@
     </row>
     <row r="201" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D201" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E201">
         <v>2467</v>
       </c>
       <c r="F201" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>10</v>
@@ -6187,16 +6190,16 @@
     </row>
     <row r="202" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D202" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E202">
         <v>2460</v>
       </c>
       <c r="F202" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>10</v>
@@ -6216,16 +6219,16 @@
     </row>
     <row r="203" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D203" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E203">
         <v>3533</v>
       </c>
       <c r="F203" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>10</v>
@@ -6245,16 +6248,16 @@
     </row>
     <row r="204" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D204" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E204">
         <v>2462</v>
       </c>
       <c r="F204" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>10</v>
@@ -6273,120 +6276,330 @@
       </c>
     </row>
     <row r="205" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H205" s="2"/>
-      <c r="I205" s="1"/>
-      <c r="J205" s="2"/>
-      <c r="K205" s="1"/>
+      <c r="D205" t="s">
+        <v>20</v>
+      </c>
+      <c r="E205">
+        <v>2464</v>
+      </c>
+      <c r="F205" t="s">
+        <v>21</v>
+      </c>
+      <c r="H205" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I205" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J205" s="2">
+        <v>0</v>
+      </c>
+      <c r="K205" s="1">
+        <v>46215.001851851855</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="206" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H206" s="2"/>
-      <c r="I206" s="1"/>
-      <c r="J206" s="2"/>
-      <c r="K206" s="1"/>
+      <c r="D206" t="s">
+        <v>20</v>
+      </c>
+      <c r="E206">
+        <v>2465</v>
+      </c>
+      <c r="F206" t="s">
+        <v>22</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I206" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J206" s="2">
+        <v>0</v>
+      </c>
+      <c r="K206" s="1">
+        <v>46215.002546296295</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+      <c r="M206" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="207" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H207" s="2"/>
-      <c r="I207" s="1"/>
-      <c r="J207" s="2"/>
-      <c r="K207" s="1"/>
+      <c r="D207" t="s">
+        <v>20</v>
+      </c>
+      <c r="E207">
+        <v>2463</v>
+      </c>
+      <c r="F207" t="s">
+        <v>23</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I207" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J207" s="2">
+        <v>0</v>
+      </c>
+      <c r="K207" s="1">
+        <v>46215.002546296295</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="M207" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="208" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H208" s="2"/>
-      <c r="I208" s="1"/>
-      <c r="J208" s="2"/>
-      <c r="K208" s="1"/>
-    </row>
-    <row r="209" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H209" s="2"/>
-      <c r="I209" s="1"/>
-      <c r="J209" s="2"/>
-      <c r="K209" s="1"/>
-    </row>
-    <row r="210" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H210" s="2"/>
-      <c r="I210" s="1"/>
-      <c r="J210" s="2"/>
-      <c r="K210" s="1"/>
-    </row>
-    <row r="211" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H211" s="2"/>
-      <c r="I211" s="1"/>
-      <c r="J211" s="2"/>
-      <c r="K211" s="1"/>
-    </row>
-    <row r="212" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D208" t="s">
+        <v>20</v>
+      </c>
+      <c r="E208">
+        <v>2468</v>
+      </c>
+      <c r="F208" t="s">
+        <v>24</v>
+      </c>
+      <c r="H208" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I208" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J208" s="2">
+        <v>0</v>
+      </c>
+      <c r="K208" s="1">
+        <v>46215.003240740742</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+      <c r="M208" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D209" t="s">
+        <v>20</v>
+      </c>
+      <c r="E209">
+        <v>2466</v>
+      </c>
+      <c r="F209" t="s">
+        <v>25</v>
+      </c>
+      <c r="H209" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I209" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J209" s="2">
+        <v>0</v>
+      </c>
+      <c r="K209" s="1">
+        <v>46215.003240740742</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
+      </c>
+      <c r="M209" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="210" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D210" t="s">
+        <v>20</v>
+      </c>
+      <c r="E210">
+        <v>2467</v>
+      </c>
+      <c r="F210" t="s">
+        <v>26</v>
+      </c>
+      <c r="H210" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I210" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J210" s="2">
+        <v>0</v>
+      </c>
+      <c r="K210" s="1">
+        <v>46215.003935185188</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+      <c r="M210" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D211" t="s">
+        <v>20</v>
+      </c>
+      <c r="E211">
+        <v>2460</v>
+      </c>
+      <c r="F211" t="s">
+        <v>27</v>
+      </c>
+      <c r="H211" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I211" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J211" s="2">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="K211" s="1">
+        <v>46215.003935185188</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+      <c r="M211" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H212" s="2"/>
       <c r="I212" s="1"/>
       <c r="J212" s="2"/>
       <c r="K212" s="1"/>
-    </row>
-    <row r="213" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H213" s="2"/>
-      <c r="I213" s="1"/>
-      <c r="J213" s="2"/>
-      <c r="K213" s="1"/>
-    </row>
-    <row r="214" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H214" s="2"/>
-      <c r="I214" s="1"/>
-      <c r="J214" s="2"/>
-      <c r="K214" s="1"/>
-    </row>
-    <row r="215" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M212" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="213" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D213" t="s">
+        <v>20</v>
+      </c>
+      <c r="E213">
+        <v>3533</v>
+      </c>
+      <c r="F213" t="s">
+        <v>37</v>
+      </c>
+      <c r="H213" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I213" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J213" s="2">
+        <v>7.8703703703703696E-3</v>
+      </c>
+      <c r="K213" s="1">
+        <v>46215.003935185188</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="214" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D214" t="s">
+        <v>20</v>
+      </c>
+      <c r="E214">
+        <v>2462</v>
+      </c>
+      <c r="F214" t="s">
+        <v>29</v>
+      </c>
+      <c r="H214" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I214" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J214" s="2">
+        <v>0</v>
+      </c>
+      <c r="K214" s="1">
+        <v>46215.004629629628</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="M214" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="215" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H215" s="2"/>
       <c r="I215" s="1"/>
       <c r="J215" s="2"/>
       <c r="K215" s="1"/>
     </row>
-    <row r="216" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="216" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H216" s="2"/>
       <c r="I216" s="1"/>
       <c r="J216" s="2"/>
       <c r="K216" s="1"/>
     </row>
-    <row r="217" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="217" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H217" s="2"/>
       <c r="I217" s="1"/>
       <c r="J217" s="2"/>
       <c r="K217" s="1"/>
     </row>
-    <row r="218" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="218" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H218" s="2"/>
       <c r="I218" s="1"/>
       <c r="J218" s="2"/>
       <c r="K218" s="1"/>
     </row>
-    <row r="219" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="219" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H219" s="2"/>
       <c r="I219" s="1"/>
       <c r="J219" s="2"/>
       <c r="K219" s="1"/>
     </row>
-    <row r="220" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="220" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H220" s="2"/>
       <c r="I220" s="1"/>
       <c r="J220" s="2"/>
       <c r="K220" s="1"/>
     </row>
-    <row r="221" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="221" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H221" s="2"/>
       <c r="I221" s="1"/>
       <c r="J221" s="2"/>
       <c r="K221" s="1"/>
     </row>
-    <row r="222" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="222" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H222" s="2"/>
       <c r="I222" s="1"/>
       <c r="J222" s="2"/>
       <c r="K222" s="1"/>
     </row>
-    <row r="223" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="223" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H223" s="2"/>
       <c r="I223" s="1"/>
       <c r="J223" s="2"/>
       <c r="K223" s="1"/>
     </row>
-    <row r="224" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="224" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H224" s="2"/>
       <c r="I224" s="1"/>
       <c r="J224" s="2"/>
@@ -9804,6 +10017,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -43455,7 +43669,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Panchos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A48747A6-6C24-467D-B934-F04DB347D941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{421AE248-7EB8-4E1B-89BB-70E6A9507B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="43">
   <si>
     <t>Company Name</t>
   </si>
@@ -541,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -6289,10 +6289,10 @@
         <v>42</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J205" s="2">
-        <v>0</v>
+        <v>7.0949074074074074E-3</v>
       </c>
       <c r="K205" s="1">
         <v>46215.001851851855</v>
@@ -6318,10 +6318,10 @@
         <v>42</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J206" s="2">
-        <v>0</v>
+        <v>8.0555555555555554E-3</v>
       </c>
       <c r="K206" s="1">
         <v>46215.002546296295</v>
@@ -6347,10 +6347,10 @@
         <v>42</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J207" s="2">
-        <v>0</v>
+        <v>7.5115740740740742E-3</v>
       </c>
       <c r="K207" s="1">
         <v>46215.002546296295</v>
@@ -6363,32 +6363,12 @@
       </c>
     </row>
     <row r="208" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D208" t="s">
-        <v>20</v>
-      </c>
-      <c r="E208">
-        <v>2468</v>
-      </c>
-      <c r="F208" t="s">
-        <v>24</v>
-      </c>
-      <c r="H208" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I208" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J208" s="2">
-        <v>0</v>
-      </c>
-      <c r="K208" s="1">
-        <v>46215.003240740742</v>
-      </c>
-      <c r="L208">
-        <v>0</v>
-      </c>
+      <c r="H208" s="2"/>
+      <c r="I208" s="1"/>
+      <c r="J208" s="2"/>
+      <c r="K208" s="1"/>
       <c r="M208" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="209" spans="4:13" x14ac:dyDescent="0.3">
@@ -6396,19 +6376,19 @@
         <v>20</v>
       </c>
       <c r="E209">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="F209" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>42</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J209" s="2">
-        <v>0</v>
+        <v>2.5462962962962961E-4</v>
       </c>
       <c r="K209" s="1">
         <v>46215.003240740742</v>
@@ -6421,32 +6401,12 @@
       </c>
     </row>
     <row r="210" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D210" t="s">
-        <v>20</v>
-      </c>
-      <c r="E210">
-        <v>2467</v>
-      </c>
-      <c r="F210" t="s">
-        <v>26</v>
-      </c>
-      <c r="H210" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I210" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J210" s="2">
-        <v>0</v>
-      </c>
-      <c r="K210" s="1">
-        <v>46215.003935185188</v>
-      </c>
-      <c r="L210">
-        <v>0</v>
-      </c>
+      <c r="H210" s="2"/>
+      <c r="I210" s="1"/>
+      <c r="J210" s="2"/>
+      <c r="K210" s="1"/>
       <c r="M210" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="211" spans="4:13" x14ac:dyDescent="0.3">
@@ -6454,22 +6414,22 @@
         <v>20</v>
       </c>
       <c r="E211">
-        <v>2460</v>
+        <v>2466</v>
       </c>
       <c r="F211" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>42</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J211" s="2">
-        <v>5.0925925925925921E-4</v>
+        <v>7.789351851851852E-3</v>
       </c>
       <c r="K211" s="1">
-        <v>46215.003935185188</v>
+        <v>46215.003240740742</v>
       </c>
       <c r="L211">
         <v>0</v>
@@ -6479,12 +6439,32 @@
       </c>
     </row>
     <row r="212" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H212" s="2"/>
-      <c r="I212" s="1"/>
-      <c r="J212" s="2"/>
-      <c r="K212" s="1"/>
+      <c r="D212" t="s">
+        <v>20</v>
+      </c>
+      <c r="E212">
+        <v>2467</v>
+      </c>
+      <c r="F212" t="s">
+        <v>26</v>
+      </c>
+      <c r="H212" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I212" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J212" s="2">
+        <v>8.1944444444444452E-3</v>
+      </c>
+      <c r="K212" s="1">
+        <v>46215.003935185188</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
       <c r="M212" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="213" spans="4:13" x14ac:dyDescent="0.3">
@@ -6492,19 +6472,19 @@
         <v>20</v>
       </c>
       <c r="E213">
-        <v>3533</v>
+        <v>2460</v>
       </c>
       <c r="F213" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>42</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J213" s="2">
-        <v>7.8703703703703696E-3</v>
+        <v>5.0925925925925921E-4</v>
       </c>
       <c r="K213" s="1">
         <v>46215.003935185188</v>
@@ -6517,45 +6497,71 @@
       </c>
     </row>
     <row r="214" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D214" t="s">
+      <c r="H214" s="2"/>
+      <c r="I214" s="1"/>
+      <c r="J214" s="2"/>
+      <c r="K214" s="1"/>
+      <c r="M214" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="215" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D215" t="s">
         <v>20</v>
       </c>
-      <c r="E214">
+      <c r="E215">
+        <v>3533</v>
+      </c>
+      <c r="F215" t="s">
+        <v>37</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I215" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J215" s="2">
+        <v>7.8703703703703696E-3</v>
+      </c>
+      <c r="K215" s="1">
+        <v>46215.003935185188</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+      <c r="M215" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="216" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D216" t="s">
+        <v>20</v>
+      </c>
+      <c r="E216">
         <v>2462</v>
       </c>
-      <c r="F214" t="s">
+      <c r="F216" t="s">
         <v>29</v>
       </c>
-      <c r="H214" s="2" t="s">
+      <c r="H216" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I214" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J214" s="2">
+      <c r="I216" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J216" s="2">
+        <v>2.2465277777777778E-2</v>
+      </c>
+      <c r="K216" s="1">
+        <v>46215.004629629628</v>
+      </c>
+      <c r="L216">
         <v>0</v>
       </c>
-      <c r="K214" s="1">
-        <v>46215.004629629628</v>
-      </c>
-      <c r="L214">
-        <v>0</v>
-      </c>
-      <c r="M214" t="s">
+      <c r="M216" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="215" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H215" s="2"/>
-      <c r="I215" s="1"/>
-      <c r="J215" s="2"/>
-      <c r="K215" s="1"/>
-    </row>
-    <row r="216" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H216" s="2"/>
-      <c r="I216" s="1"/>
-      <c r="J216" s="2"/>
-      <c r="K216" s="1"/>
     </row>
     <row r="217" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H217" s="2"/>
@@ -9946,6 +9952,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -10041,6 +10048,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -10064,6 +10072,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -10327,6 +10336,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -10338,6 +10348,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -10349,6 +10360,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -10964,6 +10976,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -11088,6 +11101,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -11230,6 +11244,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -11259,6 +11274,7 @@
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -11329,6 +11345,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -11352,6 +11369,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -11416,6 +11434,7 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
@@ -11469,6 +11488,7 @@
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -11636,6 +11656,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -11647,6 +11668,7 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
@@ -11658,6 +11680,7 @@
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -11693,6 +11716,7 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
@@ -11842,6 +11866,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -12089,6 +12114,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -12147,6 +12173,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -12205,6 +12232,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -12216,6 +12244,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -12281,6 +12310,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -12316,6 +12346,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -12381,6 +12412,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -12427,6 +12459,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -12486,6 +12519,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -12544,6 +12578,7 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
@@ -12608,6 +12643,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -12690,6 +12726,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -12753,6 +12790,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -12768,6 +12806,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -12803,6 +12842,7 @@
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -13068,6 +13108,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -13351,6 +13392,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -13368,6 +13410,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -13391,6 +13434,7 @@
     <row r="1367" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1367" s="2"/>
       <c r="I1367" s="1"/>
+      <c r="J1367" s="2"/>
       <c r="K1367" s="1"/>
     </row>
     <row r="1368" spans="8:11" x14ac:dyDescent="0.3">
@@ -13408,6 +13452,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -13740,6 +13785,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -13828,6 +13874,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -13921,6 +13968,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -13980,11 +14028,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -14036,6 +14086,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -14077,6 +14128,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -14121,6 +14173,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -14167,11 +14220,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -14369,6 +14424,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -14398,6 +14454,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -14413,6 +14471,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -14472,6 +14531,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -14543,6 +14603,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -14584,6 +14645,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -14702,6 +14764,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -14766,6 +14829,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -14890,6 +14954,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -15116,6 +15181,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -15233,6 +15299,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -15316,6 +15383,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -15375,6 +15443,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -15398,6 +15467,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -15445,6 +15515,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -15504,6 +15575,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -15527,6 +15599,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -15544,6 +15617,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -15627,6 +15701,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -15818,6 +15893,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -43674,6 +43750,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -43681,6 +43758,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -43688,6 +43766,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -43703,6 +43782,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -43712,6 +43792,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -43719,9 +43800,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -43729,12 +43816,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -43742,12 +43832,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -43759,9 +43852,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -43776,6 +43871,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -43802,6 +43898,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -43812,7 +43909,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -43820,6 +43922,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -43831,6 +43934,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -43838,6 +43942,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -43852,13 +43957,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -43869,15 +43980,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -43893,6 +44007,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -43911,6 +44026,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -43922,6 +44038,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -43939,18 +44056,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -43979,6 +44101,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -43986,9 +44109,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -44011,12 +44136,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -44031,9 +44159,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -44049,12 +44179,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -44075,6 +44207,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -44086,9 +44219,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -44100,6 +44235,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -44139,9 +44275,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -44149,9 +44287,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -44162,6 +44302,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -44169,18 +44310,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -44188,6 +44337,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -44198,6 +44348,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -44224,15 +44375,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -44254,6 +44409,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -44261,9 +44417,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -44271,6 +44429,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -44282,6 +44441,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -44296,6 +44456,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -44305,6 +44469,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -44316,6 +44481,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -44326,10 +44492,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -44337,6 +44508,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -44351,6 +44523,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -44373,6 +44546,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -44392,25 +44566,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -44418,6 +44604,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -44425,15 +44612,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -44447,6 +44641,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -44465,9 +44660,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -44475,9 +44672,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -44485,6 +44684,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -44501,10 +44701,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Panchos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BE5BB1C-8E9C-47FD-848E-2B4D2E0AE2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D3ED63D-B07A-478A-8A26-A01BED3C0A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="44">
   <si>
     <t>Company Name</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>(SP) 3 Points of Contact</t>
+  </si>
+  <si>
+    <t>Speed Managment (SP)</t>
   </si>
 </sst>
 </file>
@@ -541,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7404"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -556,39 +559,39 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>21</v>
       </c>
@@ -617,7 +620,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>21</v>
       </c>
@@ -646,7 +649,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -675,7 +678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>21</v>
       </c>
@@ -704,7 +707,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>21</v>
       </c>
@@ -733,7 +736,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>21</v>
       </c>
@@ -762,7 +765,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>21</v>
       </c>
@@ -791,7 +794,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>21</v>
       </c>
@@ -820,7 +823,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>21</v>
       </c>
@@ -849,7 +852,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>21</v>
       </c>
@@ -878,7 +881,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>21</v>
       </c>
@@ -907,7 +910,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>21</v>
       </c>
@@ -936,7 +939,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>21</v>
       </c>
@@ -965,7 +968,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>21</v>
       </c>
@@ -994,7 +997,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>21</v>
       </c>
@@ -6527,58 +6530,265 @@
       </c>
     </row>
     <row r="214" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H214" s="2"/>
-      <c r="I214" s="1"/>
-      <c r="J214" s="2"/>
-      <c r="K214" s="1"/>
+      <c r="B214" t="s">
+        <v>21</v>
+      </c>
+      <c r="C214">
+        <v>2464</v>
+      </c>
+      <c r="D214" t="s">
+        <v>22</v>
+      </c>
+      <c r="F214" t="s">
+        <v>43</v>
+      </c>
+      <c r="G214" t="s">
+        <v>10</v>
+      </c>
+      <c r="H214" s="2">
+        <v>8.7500000000000008E-3</v>
+      </c>
+      <c r="I214" s="1">
+        <v>46237.801851851851</v>
+      </c>
+      <c r="J214" s="2">
+        <v>0</v>
+      </c>
+      <c r="K214" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="215" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H215" s="2"/>
-      <c r="I215" s="1"/>
-      <c r="J215" s="2"/>
-      <c r="K215" s="1"/>
+      <c r="B215" t="s">
+        <v>21</v>
+      </c>
+      <c r="C215">
+        <v>2465</v>
+      </c>
+      <c r="D215" t="s">
+        <v>23</v>
+      </c>
+      <c r="F215" t="s">
+        <v>43</v>
+      </c>
+      <c r="G215" t="s">
+        <v>10</v>
+      </c>
+      <c r="H215" s="2">
+        <v>1.0219907407407407E-2</v>
+      </c>
+      <c r="I215" s="1">
+        <v>46237.802546296298</v>
+      </c>
+      <c r="J215" s="2">
+        <v>0</v>
+      </c>
+      <c r="K215" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="216" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H216" s="2"/>
-      <c r="I216" s="1"/>
-      <c r="J216" s="2"/>
-      <c r="K216" s="1"/>
+      <c r="B216" t="s">
+        <v>21</v>
+      </c>
+      <c r="C216">
+        <v>2463</v>
+      </c>
+      <c r="D216" t="s">
+        <v>24</v>
+      </c>
+      <c r="F216" t="s">
+        <v>43</v>
+      </c>
+      <c r="G216" t="s">
+        <v>10</v>
+      </c>
+      <c r="H216" s="2">
+        <v>1.1273148148148148E-2</v>
+      </c>
+      <c r="I216" s="1">
+        <v>46237.803240740737</v>
+      </c>
+      <c r="J216" s="2">
+        <v>0</v>
+      </c>
+      <c r="K216" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="217" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H217" s="2"/>
-      <c r="I217" s="1"/>
-      <c r="J217" s="2"/>
-      <c r="K217" s="1"/>
+      <c r="B217" t="s">
+        <v>21</v>
+      </c>
+      <c r="C217">
+        <v>2468</v>
+      </c>
+      <c r="D217" t="s">
+        <v>25</v>
+      </c>
+      <c r="F217" t="s">
+        <v>43</v>
+      </c>
+      <c r="G217" t="s">
+        <v>10</v>
+      </c>
+      <c r="H217" s="2">
+        <v>1.0081018518518519E-2</v>
+      </c>
+      <c r="I217" s="1">
+        <v>46237.803935185184</v>
+      </c>
+      <c r="J217" s="2">
+        <v>0</v>
+      </c>
+      <c r="K217" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="218" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H218" s="2"/>
-      <c r="I218" s="1"/>
-      <c r="J218" s="2"/>
-      <c r="K218" s="1"/>
+      <c r="B218" t="s">
+        <v>21</v>
+      </c>
+      <c r="C218">
+        <v>2466</v>
+      </c>
+      <c r="D218" t="s">
+        <v>26</v>
+      </c>
+      <c r="F218" t="s">
+        <v>43</v>
+      </c>
+      <c r="G218" t="s">
+        <v>10</v>
+      </c>
+      <c r="H218" s="2">
+        <v>8.2175925925925923E-3</v>
+      </c>
+      <c r="I218" s="1">
+        <v>46237.803935185184</v>
+      </c>
+      <c r="J218" s="2">
+        <v>0</v>
+      </c>
+      <c r="K218" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="219" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H219" s="2"/>
-      <c r="I219" s="1"/>
-      <c r="J219" s="2"/>
-      <c r="K219" s="1"/>
+      <c r="B219" t="s">
+        <v>21</v>
+      </c>
+      <c r="C219">
+        <v>2467</v>
+      </c>
+      <c r="D219" t="s">
+        <v>27</v>
+      </c>
+      <c r="F219" t="s">
+        <v>43</v>
+      </c>
+      <c r="G219" t="s">
+        <v>10</v>
+      </c>
+      <c r="H219" s="2">
+        <v>1.0960648148148148E-2</v>
+      </c>
+      <c r="I219" s="1">
+        <v>46237.804629629631</v>
+      </c>
+      <c r="J219" s="2">
+        <v>0</v>
+      </c>
+      <c r="K219" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="220" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H220" s="2"/>
-      <c r="I220" s="1"/>
-      <c r="J220" s="2"/>
-      <c r="K220" s="1"/>
+      <c r="B220" t="s">
+        <v>21</v>
+      </c>
+      <c r="C220">
+        <v>2460</v>
+      </c>
+      <c r="D220" t="s">
+        <v>28</v>
+      </c>
+      <c r="F220" t="s">
+        <v>43</v>
+      </c>
+      <c r="G220" t="s">
+        <v>10</v>
+      </c>
+      <c r="H220" s="2">
+        <v>5.0451388888888886E-2</v>
+      </c>
+      <c r="I220" s="1">
+        <v>46237.805324074077</v>
+      </c>
+      <c r="J220" s="2">
+        <v>0</v>
+      </c>
+      <c r="K220" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="221" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H221" s="2"/>
-      <c r="I221" s="1"/>
-      <c r="J221" s="2"/>
-      <c r="K221" s="1"/>
+      <c r="B221" t="s">
+        <v>21</v>
+      </c>
+      <c r="C221">
+        <v>3533</v>
+      </c>
+      <c r="D221" t="s">
+        <v>38</v>
+      </c>
+      <c r="F221" t="s">
+        <v>43</v>
+      </c>
+      <c r="G221" t="s">
+        <v>10</v>
+      </c>
+      <c r="H221" s="2">
+        <v>9.1782407407407403E-3</v>
+      </c>
+      <c r="I221" s="1">
+        <v>46237.805324074077</v>
+      </c>
+      <c r="J221" s="2">
+        <v>0</v>
+      </c>
+      <c r="K221" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="222" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H222" s="2"/>
-      <c r="I222" s="1"/>
-      <c r="J222" s="2"/>
-      <c r="K222" s="1"/>
+      <c r="B222" t="s">
+        <v>21</v>
+      </c>
+      <c r="C222">
+        <v>2462</v>
+      </c>
+      <c r="D222" t="s">
+        <v>30</v>
+      </c>
+      <c r="F222" t="s">
+        <v>43</v>
+      </c>
+      <c r="G222" t="s">
+        <v>10</v>
+      </c>
+      <c r="H222" s="2">
+        <v>8.3680555555555557E-3</v>
+      </c>
+      <c r="I222" s="1">
+        <v>46237.806018518517</v>
+      </c>
+      <c r="J222" s="2">
+        <v>0</v>
+      </c>
+      <c r="K222" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="223" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H223" s="2"/>
@@ -11333,7 +11543,6 @@
       <c r="K1014" s="1"/>
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1015" s="2"/>
       <c r="I1015" s="1"/>
       <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
@@ -11423,7 +11632,6 @@
       <c r="K1029" s="1"/>
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1030" s="2"/>
       <c r="I1030" s="1"/>
       <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
@@ -12782,7 +12990,6 @@
       <c r="K1257" s="1"/>
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1258" s="2"/>
       <c r="I1258" s="1"/>
       <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
@@ -12799,7 +13006,6 @@
       <c r="K1260" s="1"/>
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1261" s="2"/>
       <c r="I1261" s="1"/>
       <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
@@ -14094,7 +14300,6 @@
       <c r="K1477" s="1"/>
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1478" s="2"/>
       <c r="I1478" s="1"/>
       <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
@@ -14182,7 +14387,6 @@
       <c r="K1492" s="1"/>
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1493" s="2"/>
       <c r="I1493" s="1"/>
       <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
@@ -16824,7 +17028,6 @@
       <c r="K1933" s="1"/>
     </row>
     <row r="1934" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1934" s="2"/>
       <c r="I1934" s="1"/>
       <c r="K1934" s="1"/>
     </row>
@@ -16844,7 +17047,6 @@
       <c r="K1937" s="1"/>
     </row>
     <row r="1938" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H1938" s="2"/>
       <c r="I1938" s="1"/>
       <c r="K1938" s="1"/>
     </row>
@@ -47384,6 +47586,7 @@
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
@@ -47398,11 +47601,13 @@
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -47413,10 +47618,13 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
@@ -47434,14 +47642,17 @@
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -47452,14 +47663,17 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
@@ -47486,6 +47700,7 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
@@ -47494,6 +47709,7 @@
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
@@ -47506,22 +47722,27 @@
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -47540,6 +47761,7 @@
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -47550,10 +47772,12 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
@@ -47562,10 +47786,12 @@
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
@@ -47579,82 +47805,97 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
@@ -47668,6 +47909,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -47678,6 +47920,7 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
@@ -47685,6 +47928,7 @@
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
@@ -47693,86 +47937,99 @@
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -47789,26 +48046,32 @@
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
@@ -47839,6 +48102,7 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
@@ -47848,10 +48112,12 @@
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
@@ -47864,14 +48130,17 @@
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
@@ -47880,14 +48149,17 @@
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
@@ -47906,26 +48178,32 @@
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -47944,6 +48222,7 @@
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
@@ -47952,10 +48231,12 @@
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
@@ -47964,6 +48245,7 @@
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
@@ -47976,10 +48258,12 @@
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
@@ -47988,6 +48272,7 @@
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
@@ -47996,14 +48281,17 @@
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
@@ -48012,14 +48300,17 @@
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
@@ -48036,76 +48327,85 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
@@ -48119,31 +48419,38 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
@@ -48156,10 +48463,12 @@
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
@@ -48168,10 +48477,12 @@
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
@@ -48180,6 +48491,7 @@
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -48194,10 +48506,12 @@
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
@@ -48206,10 +48520,12 @@
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
@@ -48223,6 +48539,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -48238,14 +48555,17 @@
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -48263,14 +48583,17 @@
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
@@ -48283,10 +48606,12 @@
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
@@ -48295,14 +48620,17 @@
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
@@ -48311,10 +48639,12 @@
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
@@ -48323,14 +48653,17 @@
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
@@ -48352,6 +48685,7 @@
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
@@ -48360,39 +48694,65 @@
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7395" s="2"/>
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
+    </row>
+    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7402" s="2"/>
+      <c r="I7402" s="1"/>
+    </row>
+    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7403" s="1"/>
+    </row>
+    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7404" s="2"/>
+      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Panchos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D3ED63D-B07A-478A-8A26-A01BED3C0A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66E900B2-24BD-4C94-B30A-DAFD427B90B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -544,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -620,7 +620,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>21</v>
       </c>
@@ -794,7 +794,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>21</v>
       </c>
@@ -910,7 +910,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>21</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>21</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>21</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>21</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>21</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>21</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>21</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>21</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>21</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>21</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>21</v>
       </c>
@@ -5390,7 +5390,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>21</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>21</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>21</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>21</v>
       </c>
@@ -6886,7 +6886,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -7402,7 +7402,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -7468,7 +7468,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -7480,7 +7480,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -7576,7 +7576,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -7588,7 +7588,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -7684,7 +7684,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -7744,7 +7744,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -46697,6 +46697,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -46989,6 +46990,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -47299,6 +47302,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -47423,6 +47427,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -47434,6 +47439,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -47582,6 +47588,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -47592,10 +47599,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -47629,15 +47638,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -47678,18 +47690,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -47705,6 +47721,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -47714,10 +47731,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -47753,10 +47772,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -47782,6 +47803,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -47796,6 +47818,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -47830,6 +47853,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -47839,6 +47863,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -47848,6 +47873,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -47862,15 +47888,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -47900,6 +47927,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -47920,11 +47948,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -47933,6 +47963,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -47962,6 +47993,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -47971,10 +48003,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -47989,14 +48023,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -48016,10 +48053,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -48039,9 +48078,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -48076,18 +48118,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -48102,12 +48148,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -48122,10 +48168,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -48145,6 +48193,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -48164,6 +48213,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -48173,6 +48223,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -48218,6 +48269,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -48227,6 +48279,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -48241,6 +48294,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -48250,10 +48304,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -48268,6 +48324,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -48277,6 +48334,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -48296,6 +48354,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -48315,10 +48374,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -48328,6 +48389,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -48338,10 +48400,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -48356,18 +48420,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -48387,10 +48455,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -48410,6 +48480,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -48440,7 +48511,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -48455,10 +48525,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -48473,6 +48545,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -48487,11 +48560,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -48501,6 +48574,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -48516,6 +48590,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -48530,6 +48605,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -48550,6 +48626,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -48575,11 +48652,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -48598,15 +48677,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -48616,6 +48696,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -48635,6 +48716,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -48649,6 +48731,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -48668,10 +48751,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -48681,6 +48766,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -48691,6 +48777,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -48727,7 +48814,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -48736,6 +48822,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -48749,10 +48836,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Panchos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66E900B2-24BD-4C94-B30A-DAFD427B90B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F839D6BB-5E04-4CD9-A09C-615421145E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -86,13 +86,13 @@
     <t>Mark Complete</t>
   </si>
   <si>
-    <t>(Spanish) Scene of an Accident</t>
-  </si>
-  <si>
     <t>(Spanish) -Alert Driving</t>
   </si>
   <si>
     <t>(Spanish) Space Management</t>
+  </si>
+  <si>
+    <t>(Spanish) Scene of an Accident</t>
   </si>
   <si>
     <t>(Spanish) Winter Weather</t>
@@ -544,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -602,7 +602,7 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
@@ -620,7 +620,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>21</v>
       </c>
@@ -631,7 +631,7 @@
         <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
@@ -660,7 +660,7 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
@@ -689,7 +689,7 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -718,7 +718,7 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
@@ -747,7 +747,7 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
         <v>10</v>
@@ -776,7 +776,7 @@
         <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
@@ -794,7 +794,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>21</v>
       </c>
@@ -805,7 +805,7 @@
         <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
@@ -834,7 +834,7 @@
         <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
@@ -910,7 +910,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>21</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>21</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>21</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>21</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>22</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G44" t="s">
         <v>10</v>
@@ -1723,7 +1723,7 @@
         <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G45" t="s">
         <v>10</v>
@@ -1752,7 +1752,7 @@
         <v>24</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G46" t="s">
         <v>12</v>
@@ -1789,7 +1789,7 @@
         <v>25</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G48" t="s">
         <v>10</v>
@@ -1818,7 +1818,7 @@
         <v>26</v>
       </c>
       <c r="F49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G49" t="s">
         <v>10</v>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
       <c r="F50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G50" t="s">
         <v>10</v>
@@ -1876,7 +1876,7 @@
         <v>28</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -1905,7 +1905,7 @@
         <v>29</v>
       </c>
       <c r="F52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G52" t="s">
         <v>10</v>
@@ -1934,7 +1934,7 @@
         <v>30</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G53" t="s">
         <v>10</v>
@@ -1952,7 +1952,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>21</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>21</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>21</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>21</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>22</v>
       </c>
       <c r="F100" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G100" t="s">
         <v>10</v>
@@ -3326,7 +3326,7 @@
         <v>23</v>
       </c>
       <c r="F101" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G101" t="s">
         <v>10</v>
@@ -3355,7 +3355,7 @@
         <v>24</v>
       </c>
       <c r="F102" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G102" t="s">
         <v>10</v>
@@ -3384,7 +3384,7 @@
         <v>25</v>
       </c>
       <c r="F103" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G103" t="s">
         <v>10</v>
@@ -3413,7 +3413,7 @@
         <v>37</v>
       </c>
       <c r="F104" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G104" t="s">
         <v>10</v>
@@ -3442,7 +3442,7 @@
         <v>26</v>
       </c>
       <c r="F105" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G105" t="s">
         <v>10</v>
@@ -3471,7 +3471,7 @@
         <v>27</v>
       </c>
       <c r="F106" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G106" t="s">
         <v>10</v>
@@ -3500,7 +3500,7 @@
         <v>28</v>
       </c>
       <c r="F107" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G107" t="s">
         <v>10</v>
@@ -3529,7 +3529,7 @@
         <v>38</v>
       </c>
       <c r="F108" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G108" t="s">
         <v>10</v>
@@ -3558,7 +3558,7 @@
         <v>30</v>
       </c>
       <c r="F109" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G109" t="s">
         <v>10</v>
@@ -3634,7 +3634,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>21</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>21</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>21</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>22</v>
       </c>
       <c r="F148" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G148" t="s">
         <v>10</v>
@@ -4718,7 +4718,7 @@
         <v>23</v>
       </c>
       <c r="F149" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G149" t="s">
         <v>12</v>
@@ -4755,7 +4755,7 @@
         <v>24</v>
       </c>
       <c r="F151" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G151" t="s">
         <v>10</v>
@@ -4784,7 +4784,7 @@
         <v>25</v>
       </c>
       <c r="F152" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G152" t="s">
         <v>10</v>
@@ -4813,7 +4813,7 @@
         <v>26</v>
       </c>
       <c r="F153" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G153" t="s">
         <v>10</v>
@@ -4842,7 +4842,7 @@
         <v>27</v>
       </c>
       <c r="F154" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G154" t="s">
         <v>10</v>
@@ -4871,7 +4871,7 @@
         <v>28</v>
       </c>
       <c r="F155" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G155" t="s">
         <v>10</v>
@@ -4900,7 +4900,7 @@
         <v>38</v>
       </c>
       <c r="F156" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G156" t="s">
         <v>10</v>
@@ -4929,7 +4929,7 @@
         <v>30</v>
       </c>
       <c r="F157" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G157" t="s">
         <v>10</v>
@@ -5390,7 +5390,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>21</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>21</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>21</v>
       </c>
@@ -6018,7 +6018,7 @@
         <v>22</v>
       </c>
       <c r="F196" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G196" t="s">
         <v>10</v>
@@ -6047,7 +6047,7 @@
         <v>23</v>
       </c>
       <c r="F197" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G197" t="s">
         <v>10</v>
@@ -6076,7 +6076,7 @@
         <v>24</v>
       </c>
       <c r="F198" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G198" t="s">
         <v>10</v>
@@ -6105,7 +6105,7 @@
         <v>25</v>
       </c>
       <c r="F199" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G199" t="s">
         <v>10</v>
@@ -6134,7 +6134,7 @@
         <v>26</v>
       </c>
       <c r="F200" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G200" t="s">
         <v>10</v>
@@ -6163,7 +6163,7 @@
         <v>27</v>
       </c>
       <c r="F201" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G201" t="s">
         <v>10</v>
@@ -6192,7 +6192,7 @@
         <v>28</v>
       </c>
       <c r="F202" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G202" t="s">
         <v>10</v>
@@ -6221,7 +6221,7 @@
         <v>38</v>
       </c>
       <c r="F203" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G203" t="s">
         <v>10</v>
@@ -6250,7 +6250,7 @@
         <v>30</v>
       </c>
       <c r="F204" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G204" t="s">
         <v>10</v>
@@ -6326,7 +6326,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>21</v>
       </c>
@@ -6886,7 +6886,7 @@
       <c r="J238" s="2"/>
       <c r="K238" s="1"/>
     </row>
-    <row r="239" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H239" s="2"/>
       <c r="I239" s="1"/>
       <c r="J239" s="2"/>
@@ -7402,7 +7402,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -7468,7 +7468,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -7480,7 +7480,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -7576,7 +7576,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -7588,7 +7588,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -7684,7 +7684,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -7744,7 +7744,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -46697,7 +46697,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -46990,8 +46989,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -47302,7 +47299,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -47427,7 +47423,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -47439,7 +47434,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -47588,35 +47582,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -47627,44 +47615,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -47675,37 +47654,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -47716,52 +47688,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -47772,17 +47734,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -47793,32 +47752,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -47828,106 +47781,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -47937,7 +47870,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -47948,127 +47880,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -48078,62 +47984,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -48153,67 +48046,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -48223,38 +48103,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -48269,117 +48142,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -48388,99 +48238,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -48490,23 +48321,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -48515,52 +48342,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -48574,38 +48391,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -48615,7 +48425,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -48626,23 +48435,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -48652,37 +48457,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -48691,72 +48489,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -48766,76 +48550,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
